--- a/data/trans_dic/KIDMED_R3-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/KIDMED_R3-Provincia-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>38,61%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>31,53; 57,25</t>
+          <t>24,28; 43,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>22,44; 41,85</t>
+          <t>34,14; 54,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30,95; 46,84</t>
+          <t>31,87; 45,76</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>38,42%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,08; 44,17</t>
+          <t>28,19; 46,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>28,85; 46,88</t>
+          <t>31,93; 48,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24,44; 41,91</t>
+          <t>32,45; 44,95</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>59,93%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>39,1; 60,67</t>
+          <t>60,63; 78,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>58,95; 77,13</t>
+          <t>38,36; 59,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>52,61; 67,38</t>
+          <t>52,45; 67,1</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>52,02%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>60,15%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>56,1%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>48,36; 69,14</t>
+          <t>30,51; 66,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29,05; 66,88</t>
+          <t>48,95; 71,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40,27; 63,88</t>
+          <t>44,03; 65,02</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,43%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>89,02; 99,08</t>
+          <t>92,16; 100,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>92,26; 100,0</t>
+          <t>88,6; 99,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>93,65; 99,23</t>
+          <t>92,72; 99,25</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>43,2%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>25,54; 48,49</t>
+          <t>38,97; 61,11</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>39,35; 62,55</t>
+          <t>26,22; 47,8</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>36,4; 52,15</t>
+          <t>35,43; 51,38</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>70,83%</t>
+          <t>65,95%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>68,26%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>62,98; 78,27</t>
+          <t>58,38; 73,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>54,96; 73,01</t>
+          <t>63,01; 77,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>61,66; 72,9</t>
+          <t>62,83; 73,36</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,08%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>84,49; 93,94</t>
+          <t>87,46; 95,32</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>87,74; 95,46</t>
+          <t>83,8; 94,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>87,98; 93,99</t>
+          <t>87,55; 93,61</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>63,8%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>52,51; 64,56</t>
+          <t>59,91; 67,44</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>58,54; 66,47</t>
+          <t>60,58; 66,79</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>57,0; 64,34</t>
+          <t>61,22; 66,18</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>40</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>32500</t>
+          <t>20300</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24088</t>
+          <t>24174</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56588</t>
+          <t>44474</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>22516; 40880</t>
+          <t>14631; 26504</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16739; 31223</t>
+          <t>18751; 29665</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>45187; 68384</t>
+          <t>36715; 52706</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>59</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>40717</t>
+          <t>42013</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>47147</t>
+          <t>40313</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>87864</t>
+          <t>82326</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17688; 55505</t>
+          <t>32402; 53339</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>36473; 59265</t>
+          <t>31721; 48448</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>61602; 105634</t>
+          <t>69539; 96328</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>46</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>27392</t>
+          <t>40639</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>44703</t>
+          <t>26130</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>72095</t>
+          <t>66769</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>21719; 33704</t>
+          <t>34740; 45198</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>38099; 49850</t>
+          <t>20759; 31929</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>63232; 80980</t>
+          <t>58435; 74758</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>56</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>41075</t>
+          <t>36315</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>39123</t>
+          <t>42381</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>80197</t>
+          <t>78696</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>33700; 48181</t>
+          <t>21300; 46108</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>21894; 50403</t>
+          <t>34494; 50070</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>58418; 92660</t>
+          <t>61763; 91205</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>64</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>32877</t>
+          <t>38949</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>40097</t>
+          <t>34076</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>72974</t>
+          <t>73025</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>30446; 33887</t>
+          <t>36477; 39579</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>37566; 40719</t>
+          <t>31338; 35116</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>70162; 74344</t>
+          <t>69489; 74389</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>28</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>15854</t>
+          <t>23542</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>27414</t>
+          <t>15988</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>43268</t>
+          <t>39530</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>11312; 21477</t>
+          <t>18396; 28852</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>21165; 33640</t>
+          <t>11614; 21169</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>35698; 51146</t>
+          <t>32421; 47013</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>126</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>87614</t>
+          <t>92707</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>101392</t>
+          <t>86406</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>189006</t>
+          <t>179114</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>77909; 96820</t>
+          <t>82061; 102744</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>85218; 113196</t>
+          <t>76760; 94351</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>171864; 203206</t>
+          <t>164866; 192491</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>166</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>115985</t>
+          <t>144557</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>142153</t>
+          <t>124172</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>258137</t>
+          <t>268729</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>108703; 120863</t>
+          <t>137428; 149776</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>135254; 147159</t>
+          <t>115560; 129677</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>248827; 265822</t>
+          <t>258309; 276171</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>585</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>394014</t>
+          <t>439023</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>466116</t>
+          <t>393640</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>860130</t>
+          <t>832662</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>342979; 421661</t>
+          <t>411473; 463185</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>435981; 495052</t>
+          <t>374528; 412911</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>796725; 899449</t>
+          <t>798965; 863679</t>
         </is>
       </c>
     </row>
